--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1803,6 +1803,5639 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131523029</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80384</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>448180</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7037489</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131523040</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80391</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>448178</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7037487</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131524937</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Landverk, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>448113</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7037466</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131523066</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>448004</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7037485</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer här på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131524936</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>448049</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7037467</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131524938</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Landverk, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>448127</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7037481</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131524939</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80391</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>448190</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7037541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131524923</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80355</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>448029</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7037400</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Halvliggande död sälg</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131523034</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80355</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>448178</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7037486</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131523031</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80356</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>448177</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7037486</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131523033</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97888</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>448084</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7037374</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131523067</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>448029</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7037517</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131523069</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80390</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>448178</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7037491</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131524927</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>448032</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7037303</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131524924</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80356</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>448025</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7037401</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gammal låga, under död sälg med lunglav</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131524932</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>448026</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7037380</v>
+      </c>
+      <c r="S27" t="n">
+        <v>22</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131523059</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>448126</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7037416</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131523041</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80391</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>448051</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7037306</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131523035</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80355</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>448050</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7037306</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131524919</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>448031</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7037527</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131523030</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80384</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>447993</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7037446</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en klen rönn.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131524935</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80355</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>448054</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7037460</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På liten torraka av rönn.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131523065</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>447990</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7037451</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131523049</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>447992</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7037352</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131523068</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>448070</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7037546</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131523060</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>448041</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7037312</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växer här på en storvuxen gran.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131524920</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58047</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>448020</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7037494</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131523036</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80355</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>447991</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7037445</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På en klen rönn.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131523046</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57067</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>448205</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7037576</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131523056</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>448159</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7037520</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131523048</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>448085</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7037455</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131523024</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>448005</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7037334</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131524933</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80391</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>448027</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7037403</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131523055</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>448153</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7037556</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131524925</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>448020</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7037318</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131523061</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>448093</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7037386</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131523047</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57067</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>448216</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7037540</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131523032</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80356</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>448050</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7037306</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en rönn.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131523037</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80391</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>448183</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7037535</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På en sälg.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131523058</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>448064</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7037447</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131523062</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>448071</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7037345</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131523026</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92540</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>448028</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7037351</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I stambasen av en levande/döende gran.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131523054</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>448187</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7037574</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131524934</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>448037</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7037451</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131524921</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91838</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>448016</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7037409</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131523039</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80391</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>448193</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7037544</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På en rönnlåga.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -2075,7 +2075,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131524937</v>
+        <v>131523066</v>
       </c>
       <c r="B14" t="n">
         <v>79250</v>
@@ -2104,19 +2104,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448113</v>
+        <v>448004</v>
       </c>
       <c r="R14" t="n">
-        <v>7037466</v>
+        <v>7037485</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2143,19 +2146,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:25</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer här på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,25 +2162,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131523066</v>
+        <v>131524937</v>
       </c>
       <c r="B15" t="n">
         <v>79250</v>
@@ -2211,22 +2235,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448004</v>
+        <v>448113</v>
       </c>
       <c r="R15" t="n">
-        <v>7037485</v>
+        <v>7037466</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,14 +2274,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer här på flera granar.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,44 +2295,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131524925</v>
+        <v>131523061</v>
       </c>
       <c r="B46" t="n">
         <v>79250</v>
@@ -5995,19 +5995,22 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448020</v>
+        <v>448093</v>
       </c>
       <c r="R46" t="n">
-        <v>7037318</v>
+        <v>7037386</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6034,54 +6037,65 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131523061</v>
+        <v>131523047</v>
       </c>
       <c r="B47" t="n">
-        <v>79250</v>
+        <v>57067</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6089,26 +6103,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6116,10 +6135,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448093</v>
+        <v>448216</v>
       </c>
       <c r="R47" t="n">
-        <v>7037386</v>
+        <v>7037540</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6154,13 +6173,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6169,24 +6192,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6204,10 +6212,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131523047</v>
+        <v>131524925</v>
       </c>
       <c r="B48" t="n">
-        <v>57067</v>
+        <v>79250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6215,45 +6223,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448216</v>
+        <v>448020</v>
       </c>
       <c r="R48" t="n">
-        <v>7037540</v>
+        <v>7037318</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6280,14 +6280,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6298,26 +6308,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>131523029</v>
       </c>
       <c r="B12" t="n">
-        <v>80384</v>
+        <v>80387</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>131523040</v>
       </c>
       <c r="B13" t="n">
-        <v>80391</v>
+        <v>80394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131523066</v>
+        <v>131524937</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,22 +2104,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448004</v>
+        <v>448113</v>
       </c>
       <c r="R14" t="n">
-        <v>7037485</v>
+        <v>7037466</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,14 +2143,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer här på flera granar.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,54 +2164,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131524937</v>
+        <v>131523066</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,19 +2211,22 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448113</v>
+        <v>448004</v>
       </c>
       <c r="R15" t="n">
-        <v>7037466</v>
+        <v>7037485</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2274,19 +2253,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:25</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer här på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,28 +2269,54 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131524936</v>
+        <v>131524938</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,17 +2344,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448049</v>
+        <v>448127</v>
       </c>
       <c r="R16" t="n">
-        <v>7037467</v>
+        <v>7037481</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131524938</v>
+        <v>131524923</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,34 +2436,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448127</v>
+        <v>448029</v>
       </c>
       <c r="R17" t="n">
-        <v>7037481</v>
+        <v>7037400</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Halvliggande död sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,7 +2540,7 @@
         <v>131524939</v>
       </c>
       <c r="B18" t="n">
-        <v>80391</v>
+        <v>80394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131524923</v>
+        <v>131524936</v>
       </c>
       <c r="B19" t="n">
-        <v>80355</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448029</v>
+        <v>448049</v>
       </c>
       <c r="R19" t="n">
-        <v>7037400</v>
+        <v>7037467</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Halvliggande död sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523034</v>
+        <v>131523031</v>
       </c>
       <c r="B20" t="n">
-        <v>80355</v>
+        <v>80359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,26 +2772,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2799,7 +2803,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448178</v>
+        <v>448177</v>
       </c>
       <c r="R20" t="n">
         <v>7037486</v>
@@ -2839,7 +2843,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Växer här på en grovbarkad gammal sälg.</t>
+          <t>På en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2896,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523031</v>
+        <v>131523034</v>
       </c>
       <c r="B21" t="n">
-        <v>80356</v>
+        <v>80358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,30 +2907,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448177</v>
+        <v>448178</v>
       </c>
       <c r="R21" t="n">
         <v>7037486</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en grovbarkad gammal sälg.</t>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3027,38 +3027,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131523033</v>
+        <v>131523067</v>
       </c>
       <c r="B22" t="n">
-        <v>97888</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3066,10 +3065,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448084</v>
+        <v>448029</v>
       </c>
       <c r="R22" t="n">
-        <v>7037374</v>
+        <v>7037517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3117,6 +3116,21 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3134,37 +3148,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523067</v>
+        <v>131523033</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>97891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3172,10 +3187,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448029</v>
+        <v>448084</v>
       </c>
       <c r="R23" t="n">
-        <v>7037517</v>
+        <v>7037374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3223,21 +3238,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
         <v>131523069</v>
       </c>
       <c r="B24" t="n">
-        <v>80390</v>
+        <v>80393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131524927</v>
+        <v>131524924</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>80359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448032</v>
+        <v>448025</v>
       </c>
       <c r="R25" t="n">
-        <v>7037303</v>
+        <v>7037401</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Gammal låga, under död sälg med lunglav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131524924</v>
+        <v>131523059</v>
       </c>
       <c r="B26" t="n">
-        <v>80356</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3513,37 +3513,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448025</v>
+        <v>448126</v>
       </c>
       <c r="R26" t="n">
-        <v>7037401</v>
+        <v>7037416</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3570,54 +3573,60 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gammal låga, under död sälg med lunglav</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131524932</v>
+        <v>131524927</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3649,13 +3658,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448026</v>
+        <v>448032</v>
       </c>
       <c r="R27" t="n">
-        <v>7037380</v>
+        <v>7037303</v>
       </c>
       <c r="S27" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3684,7 +3693,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,7 +3703,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,37 +3735,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131523059</v>
+        <v>131523041</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>80394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3759,10 +3777,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448126</v>
+        <v>448051</v>
       </c>
       <c r="R28" t="n">
-        <v>7037416</v>
+        <v>7037306</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3797,6 +3815,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3814,17 +3837,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3842,55 +3870,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131523041</v>
+        <v>131524932</v>
       </c>
       <c r="B29" t="n">
-        <v>80391</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448051</v>
+        <v>448026</v>
       </c>
       <c r="R29" t="n">
-        <v>7037306</v>
+        <v>7037380</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3917,14 +3938,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På en rönn.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3933,54 +3959,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131523035</v>
+        <v>131524919</v>
       </c>
       <c r="B30" t="n">
-        <v>80355</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3988,40 +3988,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448050</v>
+        <v>448031</v>
       </c>
       <c r="R30" t="n">
-        <v>7037306</v>
+        <v>7037527</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4048,14 +4045,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en rönn.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4064,54 +4071,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131524919</v>
+        <v>131523035</v>
       </c>
       <c r="B31" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4119,37 +4100,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448031</v>
+        <v>448050</v>
       </c>
       <c r="R31" t="n">
-        <v>7037527</v>
+        <v>7037306</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4176,24 +4160,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4202,18 +4176,44 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4223,7 +4223,7 @@
         <v>131523030</v>
       </c>
       <c r="B32" t="n">
-        <v>80384</v>
+        <v>80387</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>131524935</v>
       </c>
       <c r="B33" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131523065</v>
+        <v>131523049</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>91817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4478,26 +4478,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4505,10 +4509,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447990</v>
+        <v>447992</v>
       </c>
       <c r="R34" t="n">
-        <v>7037451</v>
+        <v>7037352</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4545,7 +4549,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4598,10 +4602,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131523049</v>
+        <v>131523065</v>
       </c>
       <c r="B35" t="n">
-        <v>91814</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4609,30 +4613,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447992</v>
+        <v>447990</v>
       </c>
       <c r="R35" t="n">
-        <v>7037352</v>
+        <v>7037451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
+          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4736,7 +4736,7 @@
         <v>131523068</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>131523060</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>131524920</v>
       </c>
       <c r="B38" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>131523036</v>
       </c>
       <c r="B39" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523046</v>
+        <v>131523056</v>
       </c>
       <c r="B40" t="n">
-        <v>57067</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5243,31 +5243,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448205</v>
+        <v>448159</v>
       </c>
       <c r="R40" t="n">
-        <v>7037576</v>
+        <v>7037520</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5313,17 +5308,13 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5332,9 +5323,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5352,51 +5353,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131523056</v>
+        <v>131524933</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>80394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448159</v>
+        <v>448027</v>
       </c>
       <c r="R41" t="n">
-        <v>7037520</v>
+        <v>7037403</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5423,60 +5421,49 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131523048</v>
+        <v>131523046</v>
       </c>
       <c r="B42" t="n">
-        <v>91814</v>
+        <v>57070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5484,28 +5471,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5515,10 +5503,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448085</v>
+        <v>448205</v>
       </c>
       <c r="R42" t="n">
-        <v>7037455</v>
+        <v>7037576</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5555,7 +5543,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5564,7 +5552,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5573,24 +5560,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5608,10 +5580,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523024</v>
+        <v>131523048</v>
       </c>
       <c r="B43" t="n">
-        <v>91818</v>
+        <v>91817</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5619,21 +5591,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5650,10 +5622,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448005</v>
+        <v>448085</v>
       </c>
       <c r="R43" t="n">
-        <v>7037334</v>
+        <v>7037455</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5688,6 +5660,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5715,12 +5692,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5738,48 +5715,55 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131524933</v>
+        <v>131523024</v>
       </c>
       <c r="B44" t="n">
-        <v>80391</v>
+        <v>91821</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448027</v>
+        <v>448005</v>
       </c>
       <c r="R44" t="n">
-        <v>7037403</v>
+        <v>7037334</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5806,39 +5790,55 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
         <v>131523055</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>131523061</v>
       </c>
       <c r="B46" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131523047</v>
+        <v>131524925</v>
       </c>
       <c r="B47" t="n">
-        <v>57067</v>
+        <v>79253</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6103,45 +6103,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448216</v>
+        <v>448020</v>
       </c>
       <c r="R47" t="n">
-        <v>7037540</v>
+        <v>7037318</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6168,14 +6160,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6186,36 +6188,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131524925</v>
+        <v>131523047</v>
       </c>
       <c r="B48" t="n">
-        <v>79250</v>
+        <v>57070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6223,37 +6215,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448020</v>
+        <v>448216</v>
       </c>
       <c r="R48" t="n">
-        <v>7037318</v>
+        <v>7037540</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6280,24 +6280,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6308,53 +6298,67 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131523032</v>
+        <v>131523037</v>
       </c>
       <c r="B49" t="n">
-        <v>80356</v>
+        <v>80394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6362,10 +6366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448050</v>
+        <v>448183</v>
       </c>
       <c r="R49" t="n">
-        <v>7037306</v>
+        <v>7037535</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6402,7 +6406,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en rönn.</t>
+          <t>På en sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6422,12 +6426,12 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -6437,7 +6441,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6455,41 +6459,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131523037</v>
+        <v>131523032</v>
       </c>
       <c r="B50" t="n">
-        <v>80391</v>
+        <v>80359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448183</v>
+        <v>448050</v>
       </c>
       <c r="R50" t="n">
-        <v>7037535</v>
+        <v>7037306</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en sälg.</t>
+          <t>Enstaka bålar på en rönn.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131523058</v>
+        <v>131523054</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448064</v>
+        <v>448187</v>
       </c>
       <c r="R51" t="n">
-        <v>7037447</v>
+        <v>7037574</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6711,10 +6711,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131523062</v>
+        <v>131523058</v>
       </c>
       <c r="B52" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448071</v>
+        <v>448064</v>
       </c>
       <c r="R52" t="n">
-        <v>7037345</v>
+        <v>7037447</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6812,14 +6812,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6837,41 +6832,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523026</v>
+        <v>131523062</v>
       </c>
       <c r="B53" t="n">
-        <v>92540</v>
+        <v>79253</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6879,10 +6870,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448028</v>
+        <v>448071</v>
       </c>
       <c r="R53" t="n">
-        <v>7037351</v>
+        <v>7037345</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6917,11 +6908,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>I stambasen av en levande/döende gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6949,12 +6935,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6972,37 +6958,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131523054</v>
+        <v>131523026</v>
       </c>
       <c r="B54" t="n">
-        <v>79250</v>
+        <v>92543</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7010,10 +7000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448187</v>
+        <v>448028</v>
       </c>
       <c r="R54" t="n">
-        <v>7037574</v>
+        <v>7037351</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7048,6 +7038,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I stambasen av en levande/döende gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7073,9 +7068,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
         <v>131524934</v>
       </c>
       <c r="B55" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>131524921</v>
       </c>
       <c r="B56" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>131523039</v>
       </c>
       <c r="B57" t="n">
-        <v>80391</v>
+        <v>80394</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>131523029</v>
       </c>
       <c r="B12" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>131523040</v>
       </c>
       <c r="B13" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>131524937</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131523066</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>131524938</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131524923</v>
       </c>
       <c r="B17" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>131524939</v>
       </c>
       <c r="B18" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>131524936</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523031</v>
+        <v>131523034</v>
       </c>
       <c r="B20" t="n">
         <v>80359</v>
@@ -2772,30 +2772,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2803,7 +2799,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448177</v>
+        <v>448178</v>
       </c>
       <c r="R20" t="n">
         <v>7037486</v>
@@ -2843,7 +2839,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På en grovbarkad gammal sälg.</t>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2896,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523034</v>
+        <v>131523067</v>
       </c>
       <c r="B21" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,21 +2903,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2934,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448178</v>
+        <v>448029</v>
       </c>
       <c r="R21" t="n">
-        <v>7037486</v>
+        <v>7037517</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,11 +2968,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer här på en grovbarkad gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2994,22 +2985,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3027,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131523067</v>
+        <v>131523031</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>80360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,26 +3024,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3065,10 +3055,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448029</v>
+        <v>448177</v>
       </c>
       <c r="R22" t="n">
-        <v>7037517</v>
+        <v>7037486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3103,6 +3093,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3120,17 +3115,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
         <v>131523033</v>
       </c>
       <c r="B23" t="n">
-        <v>97891</v>
+        <v>97892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>131523069</v>
       </c>
       <c r="B24" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>131524924</v>
       </c>
       <c r="B25" t="n">
-        <v>80359</v>
+        <v>80360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>131523059</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>131524927</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>131523041</v>
       </c>
       <c r="B28" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>131524932</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3977,10 +3977,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131524919</v>
+        <v>131523035</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>80359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3988,37 +3988,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448031</v>
+        <v>448050</v>
       </c>
       <c r="R30" t="n">
-        <v>7037527</v>
+        <v>7037306</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4045,24 +4048,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4071,28 +4064,54 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131523035</v>
+        <v>131524919</v>
       </c>
       <c r="B31" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4100,40 +4119,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448050</v>
+        <v>448031</v>
       </c>
       <c r="R31" t="n">
-        <v>7037306</v>
+        <v>7037527</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4160,14 +4176,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en rönn.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,44 +4202,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4223,7 +4223,7 @@
         <v>131523030</v>
       </c>
       <c r="B32" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>131524935</v>
       </c>
       <c r="B33" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>131523049</v>
       </c>
       <c r="B34" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>131523065</v>
       </c>
       <c r="B35" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>131523068</v>
       </c>
       <c r="B36" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>131523060</v>
       </c>
       <c r="B37" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>131524920</v>
       </c>
       <c r="B38" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>131523036</v>
       </c>
       <c r="B39" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>131523056</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>131524933</v>
       </c>
       <c r="B41" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5460,10 +5460,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131523046</v>
+        <v>131523048</v>
       </c>
       <c r="B42" t="n">
-        <v>57070</v>
+        <v>91818</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5471,29 +5471,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5503,10 +5502,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448205</v>
+        <v>448085</v>
       </c>
       <c r="R42" t="n">
-        <v>7037576</v>
+        <v>7037455</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5543,7 +5542,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5552,6 +5551,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5560,9 +5560,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5580,10 +5595,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523048</v>
+        <v>131523024</v>
       </c>
       <c r="B43" t="n">
-        <v>91817</v>
+        <v>91822</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5591,21 +5606,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5622,10 +5637,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448085</v>
+        <v>448005</v>
       </c>
       <c r="R43" t="n">
-        <v>7037455</v>
+        <v>7037334</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5660,11 +5675,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5692,12 +5702,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5715,10 +5725,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131523024</v>
+        <v>131523046</v>
       </c>
       <c r="B44" t="n">
-        <v>91821</v>
+        <v>57071</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5726,28 +5736,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5757,10 +5768,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448005</v>
+        <v>448205</v>
       </c>
       <c r="R44" t="n">
-        <v>7037334</v>
+        <v>7037576</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5795,13 +5806,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5810,24 +5825,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
         <v>131523055</v>
       </c>
       <c r="B45" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131523061</v>
+        <v>131523047</v>
       </c>
       <c r="B46" t="n">
-        <v>79253</v>
+        <v>57071</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5977,26 +5977,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6004,10 +6009,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448093</v>
+        <v>448216</v>
       </c>
       <c r="R46" t="n">
-        <v>7037386</v>
+        <v>7037540</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6042,13 +6047,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6057,24 +6066,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6092,10 +6086,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131524925</v>
+        <v>131523061</v>
       </c>
       <c r="B47" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,19 +6115,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448020</v>
+        <v>448093</v>
       </c>
       <c r="R47" t="n">
-        <v>7037318</v>
+        <v>7037386</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6160,54 +6157,65 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131523047</v>
+        <v>131524925</v>
       </c>
       <c r="B48" t="n">
-        <v>57070</v>
+        <v>79254</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6215,45 +6223,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448216</v>
+        <v>448020</v>
       </c>
       <c r="R48" t="n">
-        <v>7037540</v>
+        <v>7037318</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6280,14 +6280,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6298,26 +6308,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
         <v>131523037</v>
       </c>
       <c r="B49" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>131523032</v>
       </c>
       <c r="B50" t="n">
-        <v>80359</v>
+        <v>80360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,10 +6590,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131523054</v>
+        <v>131523058</v>
       </c>
       <c r="B51" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448187</v>
+        <v>448064</v>
       </c>
       <c r="R51" t="n">
-        <v>7037574</v>
+        <v>7037447</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6711,10 +6711,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131523058</v>
+        <v>131523062</v>
       </c>
       <c r="B52" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448064</v>
+        <v>448071</v>
       </c>
       <c r="R52" t="n">
-        <v>7037447</v>
+        <v>7037345</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6812,9 +6812,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6832,10 +6837,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523062</v>
+        <v>131523054</v>
       </c>
       <c r="B53" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6870,10 +6875,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448071</v>
+        <v>448187</v>
       </c>
       <c r="R53" t="n">
-        <v>7037345</v>
+        <v>7037574</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6933,14 +6938,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6961,7 +6961,7 @@
         <v>131523026</v>
       </c>
       <c r="B54" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131524934</v>
+        <v>131524921</v>
       </c>
       <c r="B55" t="n">
-        <v>91821</v>
+        <v>91842</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7104,23 +7104,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7128,13 +7124,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>448037</v>
+        <v>448016</v>
       </c>
       <c r="R55" t="n">
-        <v>7037451</v>
+        <v>7037409</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7163,7 +7159,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7173,7 +7169,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7200,10 +7196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131524921</v>
+        <v>131524934</v>
       </c>
       <c r="B56" t="n">
-        <v>91841</v>
+        <v>91822</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7211,19 +7207,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>448016</v>
+        <v>448037</v>
       </c>
       <c r="R56" t="n">
-        <v>7037409</v>
+        <v>7037451</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7306,7 +7306,7 @@
         <v>131523039</v>
       </c>
       <c r="B57" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -5232,10 +5232,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523056</v>
+        <v>131523046</v>
       </c>
       <c r="B40" t="n">
-        <v>79254</v>
+        <v>57071</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5243,26 +5243,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448159</v>
+        <v>448205</v>
       </c>
       <c r="R40" t="n">
-        <v>7037520</v>
+        <v>7037576</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5308,13 +5313,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5323,19 +5332,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5353,48 +5352,51 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131524933</v>
+        <v>131523056</v>
       </c>
       <c r="B41" t="n">
-        <v>80395</v>
+        <v>79254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448027</v>
+        <v>448159</v>
       </c>
       <c r="R41" t="n">
-        <v>7037403</v>
+        <v>7037520</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5421,94 +5423,98 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131523048</v>
+        <v>131524933</v>
       </c>
       <c r="B42" t="n">
-        <v>91818</v>
+        <v>80395</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448085</v>
+        <v>448027</v>
       </c>
       <c r="R42" t="n">
-        <v>7037455</v>
+        <v>7037403</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5535,14 +5541,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5551,54 +5562,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523024</v>
+        <v>131523048</v>
       </c>
       <c r="B43" t="n">
-        <v>91822</v>
+        <v>91818</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,21 +5591,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5637,10 +5622,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448005</v>
+        <v>448085</v>
       </c>
       <c r="R43" t="n">
-        <v>7037334</v>
+        <v>7037455</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5675,6 +5660,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5702,12 +5692,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5725,10 +5715,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131523046</v>
+        <v>131523024</v>
       </c>
       <c r="B44" t="n">
-        <v>57071</v>
+        <v>91822</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5736,29 +5726,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5768,10 +5757,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448205</v>
+        <v>448005</v>
       </c>
       <c r="R44" t="n">
-        <v>7037576</v>
+        <v>7037334</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5806,17 +5795,13 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5825,9 +5810,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>131523029</v>
       </c>
       <c r="B12" t="n">
-        <v>80388</v>
+        <v>80394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>131523040</v>
       </c>
       <c r="B13" t="n">
-        <v>80395</v>
+        <v>80401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>131524937</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131523066</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131524938</v>
+        <v>131524923</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>80365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,34 +2324,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448127</v>
+        <v>448029</v>
       </c>
       <c r="R16" t="n">
-        <v>7037481</v>
+        <v>7037400</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Halvliggande död sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,32 +2425,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131524923</v>
+        <v>131524939</v>
       </c>
       <c r="B17" t="n">
-        <v>80359</v>
+        <v>80401</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448029</v>
+        <v>448190</v>
       </c>
       <c r="R17" t="n">
-        <v>7037400</v>
+        <v>7037541</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Halvliggande död sälg</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,45 +2537,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131524939</v>
+        <v>131524938</v>
       </c>
       <c r="B18" t="n">
-        <v>80395</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448190</v>
+        <v>448127</v>
       </c>
       <c r="R18" t="n">
-        <v>7037541</v>
+        <v>7037481</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,7 +2652,7 @@
         <v>131524936</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>131523034</v>
       </c>
       <c r="B20" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2892,37 +2892,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523067</v>
+        <v>131523033</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>97898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2930,10 +2931,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448029</v>
+        <v>448084</v>
       </c>
       <c r="R21" t="n">
-        <v>7037517</v>
+        <v>7037374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2981,21 +2982,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3013,10 +2999,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131523031</v>
+        <v>131523067</v>
       </c>
       <c r="B22" t="n">
-        <v>80360</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3024,30 +3010,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3055,10 +3037,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448177</v>
+        <v>448029</v>
       </c>
       <c r="R22" t="n">
-        <v>7037486</v>
+        <v>7037517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3093,11 +3075,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3115,22 +3092,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3148,38 +3120,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523033</v>
+        <v>131523031</v>
       </c>
       <c r="B23" t="n">
-        <v>97892</v>
+        <v>80366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3187,10 +3162,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448084</v>
+        <v>448177</v>
       </c>
       <c r="R23" t="n">
-        <v>7037374</v>
+        <v>7037486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3225,6 +3200,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3238,6 +3218,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
         <v>131523069</v>
       </c>
       <c r="B24" t="n">
-        <v>80394</v>
+        <v>80400</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,48 +3390,55 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131524924</v>
+        <v>131523041</v>
       </c>
       <c r="B25" t="n">
-        <v>80360</v>
+        <v>80401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448025</v>
+        <v>448051</v>
       </c>
       <c r="R25" t="n">
-        <v>7037401</v>
+        <v>7037306</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3458,24 +3465,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gammal låga, under död sälg med lunglav</t>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,18 +3481,44 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3505,7 +3528,7 @@
         <v>131523059</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3626,7 +3649,7 @@
         <v>131524927</v>
       </c>
       <c r="B27" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3735,55 +3758,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131523041</v>
+        <v>131524932</v>
       </c>
       <c r="B28" t="n">
-        <v>80395</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448051</v>
+        <v>448026</v>
       </c>
       <c r="R28" t="n">
-        <v>7037306</v>
+        <v>7037380</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3810,14 +3826,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en rönn.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,54 +3847,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131524932</v>
+        <v>131524924</v>
       </c>
       <c r="B29" t="n">
-        <v>79254</v>
+        <v>80366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3881,21 +3876,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3905,13 +3900,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448026</v>
+        <v>448025</v>
       </c>
       <c r="R29" t="n">
-        <v>7037380</v>
+        <v>7037401</v>
       </c>
       <c r="S29" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3950,7 +3945,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gammal låga, under död sälg med lunglav</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,7 +3980,7 @@
         <v>131523035</v>
       </c>
       <c r="B30" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>131524919</v>
       </c>
       <c r="B31" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>131523030</v>
       </c>
       <c r="B32" t="n">
-        <v>80388</v>
+        <v>80394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>131524935</v>
       </c>
       <c r="B33" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131523049</v>
+        <v>131523065</v>
       </c>
       <c r="B34" t="n">
-        <v>91818</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4478,30 +4478,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4509,10 +4505,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447992</v>
+        <v>447990</v>
       </c>
       <c r="R34" t="n">
-        <v>7037352</v>
+        <v>7037451</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4549,7 +4545,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
+          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4602,10 +4598,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131523065</v>
+        <v>131523049</v>
       </c>
       <c r="B35" t="n">
-        <v>79254</v>
+        <v>91824</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,26 +4609,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447990</v>
+        <v>447992</v>
       </c>
       <c r="R35" t="n">
-        <v>7037451</v>
+        <v>7037352</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4736,7 +4736,7 @@
         <v>131523068</v>
       </c>
       <c r="B36" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>131523060</v>
       </c>
       <c r="B37" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>131524920</v>
       </c>
       <c r="B38" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>131523036</v>
       </c>
       <c r="B39" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523046</v>
+        <v>131523056</v>
       </c>
       <c r="B40" t="n">
-        <v>57071</v>
+        <v>79260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5243,31 +5243,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448205</v>
+        <v>448159</v>
       </c>
       <c r="R40" t="n">
-        <v>7037576</v>
+        <v>7037520</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5313,17 +5308,13 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5332,9 +5323,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5352,10 +5353,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131523056</v>
+        <v>131523048</v>
       </c>
       <c r="B41" t="n">
-        <v>79254</v>
+        <v>91824</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5363,26 +5364,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5390,10 +5395,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448159</v>
+        <v>448085</v>
       </c>
       <c r="R41" t="n">
-        <v>7037520</v>
+        <v>7037455</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5428,6 +5433,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5453,9 +5463,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5473,48 +5488,55 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131524933</v>
+        <v>131523024</v>
       </c>
       <c r="B42" t="n">
-        <v>80395</v>
+        <v>91828</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448027</v>
+        <v>448005</v>
       </c>
       <c r="R42" t="n">
-        <v>7037403</v>
+        <v>7037334</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5541,94 +5563,103 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523048</v>
+        <v>131524933</v>
       </c>
       <c r="B43" t="n">
-        <v>91818</v>
+        <v>80401</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448085</v>
+        <v>448027</v>
       </c>
       <c r="R43" t="n">
-        <v>7037455</v>
+        <v>7037403</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5655,14 +5686,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5671,54 +5707,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131523024</v>
+        <v>131523046</v>
       </c>
       <c r="B44" t="n">
-        <v>91822</v>
+        <v>57077</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5726,28 +5736,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5757,10 +5768,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448005</v>
+        <v>448205</v>
       </c>
       <c r="R44" t="n">
-        <v>7037334</v>
+        <v>7037576</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5795,13 +5806,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5810,24 +5825,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
         <v>131523055</v>
       </c>
       <c r="B45" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131523047</v>
+        <v>131523061</v>
       </c>
       <c r="B46" t="n">
-        <v>57071</v>
+        <v>79260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5977,31 +5977,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6009,10 +6004,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448216</v>
+        <v>448093</v>
       </c>
       <c r="R46" t="n">
-        <v>7037540</v>
+        <v>7037386</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,17 +6042,13 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6066,9 +6057,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6086,10 +6092,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131523061</v>
+        <v>131524925</v>
       </c>
       <c r="B47" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6115,22 +6121,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448093</v>
+        <v>448020</v>
       </c>
       <c r="R47" t="n">
-        <v>7037386</v>
+        <v>7037318</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6157,65 +6160,54 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131524925</v>
+        <v>131523047</v>
       </c>
       <c r="B48" t="n">
-        <v>79254</v>
+        <v>57077</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6223,37 +6215,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448020</v>
+        <v>448216</v>
       </c>
       <c r="R48" t="n">
-        <v>7037318</v>
+        <v>7037540</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6280,24 +6280,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6308,16 +6298,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
         <v>131523037</v>
       </c>
       <c r="B49" t="n">
-        <v>80395</v>
+        <v>80401</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>131523032</v>
       </c>
       <c r="B50" t="n">
-        <v>80360</v>
+        <v>80366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>131523058</v>
       </c>
       <c r="B51" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>131523062</v>
       </c>
       <c r="B52" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,37 +6837,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523054</v>
+        <v>131523026</v>
       </c>
       <c r="B53" t="n">
-        <v>79254</v>
+        <v>92550</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6875,10 +6879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448187</v>
+        <v>448028</v>
       </c>
       <c r="R53" t="n">
-        <v>7037574</v>
+        <v>7037351</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6913,6 +6917,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I stambasen av en levande/döende gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6938,9 +6947,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6958,41 +6972,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131523026</v>
+        <v>131523054</v>
       </c>
       <c r="B54" t="n">
-        <v>92544</v>
+        <v>79260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7000,10 +7010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448028</v>
+        <v>448187</v>
       </c>
       <c r="R54" t="n">
-        <v>7037351</v>
+        <v>7037574</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7038,11 +7048,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I stambasen av en levande/döende gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7068,14 +7073,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
         <v>131524921</v>
       </c>
       <c r="B55" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>131524934</v>
       </c>
       <c r="B56" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>131523039</v>
       </c>
       <c r="B57" t="n">
-        <v>80395</v>
+        <v>80401</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -4733,10 +4733,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523068</v>
+        <v>131524920</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4744,40 +4744,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448070</v>
+        <v>448020</v>
       </c>
       <c r="R36" t="n">
-        <v>7037546</v>
+        <v>7037494</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4804,57 +4806,46 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523060</v>
+        <v>131523068</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4892,10 +4883,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448041</v>
+        <v>448070</v>
       </c>
       <c r="R37" t="n">
-        <v>7037312</v>
+        <v>7037546</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4930,11 +4921,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växer här på en storvuxen gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4960,14 +4946,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4985,10 +4966,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131524920</v>
+        <v>131523060</v>
       </c>
       <c r="B38" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4996,42 +4977,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448020</v>
+        <v>448041</v>
       </c>
       <c r="R38" t="n">
-        <v>7037494</v>
+        <v>7037312</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5058,19 +5037,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:23</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Växer här på en storvuxen gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5079,18 +5053,44 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -2313,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131524923</v>
+        <v>131524938</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,34 +2324,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448029</v>
+        <v>448127</v>
       </c>
       <c r="R16" t="n">
-        <v>7037400</v>
+        <v>7037481</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Halvliggande död sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,32 +2425,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131524939</v>
+        <v>131524923</v>
       </c>
       <c r="B17" t="n">
-        <v>80401</v>
+        <v>80365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448190</v>
+        <v>448029</v>
       </c>
       <c r="R17" t="n">
-        <v>7037541</v>
+        <v>7037400</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Halvliggande död sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,45 +2537,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131524938</v>
+        <v>131524939</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>80401</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448127</v>
+        <v>448190</v>
       </c>
       <c r="R18" t="n">
-        <v>7037481</v>
+        <v>7037541</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523034</v>
+        <v>131523031</v>
       </c>
       <c r="B20" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,26 +2772,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2799,7 +2803,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448178</v>
+        <v>448177</v>
       </c>
       <c r="R20" t="n">
         <v>7037486</v>
@@ -2839,7 +2843,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Växer här på en grovbarkad gammal sälg.</t>
+          <t>På en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,38 +2896,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523033</v>
+        <v>131523034</v>
       </c>
       <c r="B21" t="n">
-        <v>97898</v>
+        <v>80365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2931,10 +2934,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448084</v>
+        <v>448178</v>
       </c>
       <c r="R21" t="n">
-        <v>7037374</v>
+        <v>7037486</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,6 +2972,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2982,6 +2990,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3120,41 +3148,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523031</v>
+        <v>131523033</v>
       </c>
       <c r="B23" t="n">
-        <v>80366</v>
+        <v>97898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3162,10 +3187,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448177</v>
+        <v>448084</v>
       </c>
       <c r="R23" t="n">
-        <v>7037486</v>
+        <v>7037374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3200,11 +3225,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3218,26 +3238,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3390,55 +3390,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131523041</v>
+        <v>131524924</v>
       </c>
       <c r="B25" t="n">
-        <v>80401</v>
+        <v>80366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448051</v>
+        <v>448025</v>
       </c>
       <c r="R25" t="n">
-        <v>7037306</v>
+        <v>7037401</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3465,14 +3458,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På en rönn.</t>
+          <t>Gammal låga, under död sälg med lunglav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3481,44 +3484,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3758,48 +3735,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131524932</v>
+        <v>131523041</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>80401</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448026</v>
+        <v>448051</v>
       </c>
       <c r="R28" t="n">
-        <v>7037380</v>
+        <v>7037306</v>
       </c>
       <c r="S28" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3826,19 +3810,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3847,28 +3826,54 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131524924</v>
+        <v>131524932</v>
       </c>
       <c r="B29" t="n">
-        <v>80366</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3876,21 +3881,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3900,13 +3905,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448025</v>
+        <v>448026</v>
       </c>
       <c r="R29" t="n">
-        <v>7037401</v>
+        <v>7037380</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,12 +3950,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gammal låga, under död sälg med lunglav</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5232,10 +5232,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523056</v>
+        <v>131523046</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>57077</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5243,26 +5243,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448159</v>
+        <v>448205</v>
       </c>
       <c r="R40" t="n">
-        <v>7037520</v>
+        <v>7037576</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5308,13 +5313,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5323,19 +5332,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5618,48 +5617,51 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131524933</v>
+        <v>131523056</v>
       </c>
       <c r="B43" t="n">
-        <v>80401</v>
+        <v>79260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448027</v>
+        <v>448159</v>
       </c>
       <c r="R43" t="n">
-        <v>7037403</v>
+        <v>7037520</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5686,95 +5688,98 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131523046</v>
+        <v>131524933</v>
       </c>
       <c r="B44" t="n">
-        <v>57077</v>
+        <v>80401</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448205</v>
+        <v>448027</v>
       </c>
       <c r="R44" t="n">
-        <v>7037576</v>
+        <v>7037403</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5801,14 +5806,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5819,26 +5829,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6324,41 +6324,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131523037</v>
+        <v>131523032</v>
       </c>
       <c r="B49" t="n">
-        <v>80401</v>
+        <v>80366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6366,10 +6362,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448183</v>
+        <v>448050</v>
       </c>
       <c r="R49" t="n">
-        <v>7037535</v>
+        <v>7037306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6406,7 +6402,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en sälg.</t>
+          <t>Enstaka bålar på en rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6426,12 +6422,12 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -6441,7 +6437,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6459,37 +6455,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131523032</v>
+        <v>131523037</v>
       </c>
       <c r="B50" t="n">
-        <v>80366</v>
+        <v>80401</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448050</v>
+        <v>448183</v>
       </c>
       <c r="R50" t="n">
-        <v>7037306</v>
+        <v>7037535</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en rönn.</t>
+          <t>På en sälg.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6590,37 +6590,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131523058</v>
+        <v>131523026</v>
       </c>
       <c r="B51" t="n">
-        <v>79260</v>
+        <v>92550</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6628,10 +6632,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448064</v>
+        <v>448028</v>
       </c>
       <c r="R51" t="n">
-        <v>7037447</v>
+        <v>7037351</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6666,6 +6670,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I stambasen av en levande/döende gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6691,9 +6700,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6711,7 +6725,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131523062</v>
+        <v>131523058</v>
       </c>
       <c r="B52" t="n">
         <v>79260</v>
@@ -6749,10 +6763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448071</v>
+        <v>448064</v>
       </c>
       <c r="R52" t="n">
-        <v>7037345</v>
+        <v>7037447</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6812,14 +6826,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6837,41 +6846,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523026</v>
+        <v>131523062</v>
       </c>
       <c r="B53" t="n">
-        <v>92550</v>
+        <v>79260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6879,10 +6884,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448028</v>
+        <v>448071</v>
       </c>
       <c r="R53" t="n">
-        <v>7037351</v>
+        <v>7037345</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6917,11 +6922,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>I stambasen av en levande/döende gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6949,12 +6949,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -4467,10 +4467,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131523065</v>
+        <v>131523049</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>91824</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4478,26 +4478,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4505,10 +4509,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447990</v>
+        <v>447992</v>
       </c>
       <c r="R34" t="n">
-        <v>7037451</v>
+        <v>7037352</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4545,7 +4549,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4598,10 +4602,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131523049</v>
+        <v>131523065</v>
       </c>
       <c r="B35" t="n">
-        <v>91824</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4609,30 +4613,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447992</v>
+        <v>447990</v>
       </c>
       <c r="R35" t="n">
-        <v>7037352</v>
+        <v>7037451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
+          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4733,10 +4733,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131524920</v>
+        <v>131523068</v>
       </c>
       <c r="B36" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4744,42 +4744,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448020</v>
+        <v>448070</v>
       </c>
       <c r="R36" t="n">
-        <v>7037494</v>
+        <v>7037546</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4806,46 +4804,57 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523068</v>
+        <v>131523060</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4883,10 +4892,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448070</v>
+        <v>448041</v>
       </c>
       <c r="R37" t="n">
-        <v>7037546</v>
+        <v>7037312</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4921,6 +4930,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växer här på en storvuxen gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4946,9 +4960,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4966,10 +4985,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131523060</v>
+        <v>131524920</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4977,40 +4996,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448041</v>
+        <v>448020</v>
       </c>
       <c r="R38" t="n">
-        <v>7037312</v>
+        <v>7037494</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5037,14 +5058,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Växer här på en storvuxen gran.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5053,44 +5079,18 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -2761,41 +2761,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523031</v>
+        <v>131523033</v>
       </c>
       <c r="B20" t="n">
-        <v>80366</v>
+        <v>97899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2803,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448177</v>
+        <v>448084</v>
       </c>
       <c r="R20" t="n">
-        <v>7037486</v>
+        <v>7037374</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,11 +2838,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2859,26 +2851,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3148,38 +3120,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523033</v>
+        <v>131523031</v>
       </c>
       <c r="B23" t="n">
-        <v>97898</v>
+        <v>80366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3187,10 +3162,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448084</v>
+        <v>448177</v>
       </c>
       <c r="R23" t="n">
-        <v>7037374</v>
+        <v>7037486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3225,6 +3200,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3238,6 +3218,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131524924</v>
+        <v>131524932</v>
       </c>
       <c r="B25" t="n">
-        <v>80366</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448025</v>
+        <v>448026</v>
       </c>
       <c r="R25" t="n">
-        <v>7037401</v>
+        <v>7037380</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3470,12 +3470,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gammal låga, under död sälg med lunglav</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3502,10 +3497,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131523059</v>
+        <v>131524924</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>80366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3513,40 +3508,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448126</v>
+        <v>448025</v>
       </c>
       <c r="R26" t="n">
-        <v>7037416</v>
+        <v>7037401</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3573,57 +3565,51 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gammal låga, under död sälg med lunglav</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131524927</v>
+        <v>131523059</v>
       </c>
       <c r="B27" t="n">
         <v>79260</v>
@@ -3652,19 +3638,22 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448032</v>
+        <v>448126</v>
       </c>
       <c r="R27" t="n">
-        <v>7037303</v>
+        <v>7037416</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3691,99 +3680,98 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131523041</v>
+        <v>131524927</v>
       </c>
       <c r="B28" t="n">
-        <v>80401</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448051</v>
+        <v>448032</v>
       </c>
       <c r="R28" t="n">
-        <v>7037306</v>
+        <v>7037303</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3810,14 +3798,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en rönn.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,92 +3824,73 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131524932</v>
+        <v>131523041</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>80401</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448026</v>
+        <v>448051</v>
       </c>
       <c r="R29" t="n">
-        <v>7037380</v>
+        <v>7037306</v>
       </c>
       <c r="S29" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3938,19 +3917,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3959,18 +3933,44 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523068</v>
+        <v>131523060</v>
       </c>
       <c r="B36" t="n">
         <v>79260</v>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448070</v>
+        <v>448041</v>
       </c>
       <c r="R36" t="n">
-        <v>7037546</v>
+        <v>7037312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4809,6 +4809,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växer här på en storvuxen gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4834,9 +4839,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4854,7 +4864,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523060</v>
+        <v>131523068</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4892,10 +4902,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448041</v>
+        <v>448070</v>
       </c>
       <c r="R37" t="n">
-        <v>7037312</v>
+        <v>7037546</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4930,11 +4940,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växer här på en storvuxen gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4960,14 +4965,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131523061</v>
+        <v>131524925</v>
       </c>
       <c r="B46" t="n">
         <v>79260</v>
@@ -5995,22 +5995,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448093</v>
+        <v>448020</v>
       </c>
       <c r="R46" t="n">
-        <v>7037386</v>
+        <v>7037318</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6037,62 +6034,51 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131524925</v>
+        <v>131523061</v>
       </c>
       <c r="B47" t="n">
         <v>79260</v>
@@ -6121,19 +6107,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448020</v>
+        <v>448093</v>
       </c>
       <c r="R47" t="n">
-        <v>7037318</v>
+        <v>7037386</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6160,44 +6149,55 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6324,37 +6324,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131523032</v>
+        <v>131523037</v>
       </c>
       <c r="B49" t="n">
-        <v>80366</v>
+        <v>80401</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6362,10 +6366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448050</v>
+        <v>448183</v>
       </c>
       <c r="R49" t="n">
-        <v>7037306</v>
+        <v>7037535</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6402,7 +6406,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en rönn.</t>
+          <t>På en sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6422,12 +6426,12 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -6437,7 +6441,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6455,41 +6459,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131523037</v>
+        <v>131523032</v>
       </c>
       <c r="B50" t="n">
-        <v>80401</v>
+        <v>80366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448183</v>
+        <v>448050</v>
       </c>
       <c r="R50" t="n">
-        <v>7037535</v>
+        <v>7037306</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en sälg.</t>
+          <t>Enstaka bålar på en rönn.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6590,41 +6590,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131523026</v>
+        <v>131523058</v>
       </c>
       <c r="B51" t="n">
-        <v>92550</v>
+        <v>79260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6632,10 +6628,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448028</v>
+        <v>448064</v>
       </c>
       <c r="R51" t="n">
-        <v>7037351</v>
+        <v>7037447</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6670,11 +6666,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I stambasen av en levande/döende gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6700,14 +6691,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6725,7 +6711,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131523058</v>
+        <v>131523062</v>
       </c>
       <c r="B52" t="n">
         <v>79260</v>
@@ -6763,10 +6749,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448064</v>
+        <v>448071</v>
       </c>
       <c r="R52" t="n">
-        <v>7037447</v>
+        <v>7037345</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6826,9 +6812,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6846,7 +6837,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523062</v>
+        <v>131523054</v>
       </c>
       <c r="B53" t="n">
         <v>79260</v>
@@ -6884,10 +6875,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448071</v>
+        <v>448187</v>
       </c>
       <c r="R53" t="n">
-        <v>7037345</v>
+        <v>7037574</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6947,14 +6938,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6972,37 +6958,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131523054</v>
+        <v>131523026</v>
       </c>
       <c r="B54" t="n">
-        <v>79260</v>
+        <v>92551</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7010,10 +7000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448187</v>
+        <v>448028</v>
       </c>
       <c r="R54" t="n">
-        <v>7037574</v>
+        <v>7037351</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7048,6 +7038,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I stambasen av en levande/döende gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7073,9 +7068,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>131523029</v>
       </c>
       <c r="B12" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>131523040</v>
       </c>
       <c r="B13" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>131524937</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131523066</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>131524938</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>131524923</v>
       </c>
       <c r="B17" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>131524939</v>
       </c>
       <c r="B18" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>131524936</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>131523033</v>
       </c>
       <c r="B20" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>131523034</v>
       </c>
       <c r="B21" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>131523067</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>131523031</v>
       </c>
       <c r="B23" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>131523069</v>
       </c>
       <c r="B24" t="n">
-        <v>80400</v>
+        <v>80401</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131524932</v>
+        <v>131524924</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>80367</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,21 +3401,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448026</v>
+        <v>448025</v>
       </c>
       <c r="R25" t="n">
-        <v>7037380</v>
+        <v>7037401</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3470,7 +3470,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gammal låga, under död sälg med lunglav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3497,10 +3502,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131524924</v>
+        <v>131523059</v>
       </c>
       <c r="B26" t="n">
-        <v>80366</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,37 +3513,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448025</v>
+        <v>448126</v>
       </c>
       <c r="R26" t="n">
-        <v>7037401</v>
+        <v>7037416</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3565,54 +3573,60 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gammal låga, under död sälg med lunglav</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131523059</v>
+        <v>131524927</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,22 +3652,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448126</v>
+        <v>448032</v>
       </c>
       <c r="R27" t="n">
-        <v>7037416</v>
+        <v>7037303</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3680,98 +3691,99 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131524927</v>
+        <v>131523041</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>80402</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448032</v>
+        <v>448051</v>
       </c>
       <c r="R28" t="n">
-        <v>7037303</v>
+        <v>7037306</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3798,24 +3810,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3824,73 +3826,92 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131523041</v>
+        <v>131524932</v>
       </c>
       <c r="B29" t="n">
-        <v>80401</v>
+        <v>79261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448051</v>
+        <v>448026</v>
       </c>
       <c r="R29" t="n">
-        <v>7037306</v>
+        <v>7037380</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3917,14 +3938,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På en rönn.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3933,44 +3959,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
         <v>131523035</v>
       </c>
       <c r="B30" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>131524919</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>131523030</v>
       </c>
       <c r="B32" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>131524935</v>
       </c>
       <c r="B33" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>131523049</v>
       </c>
       <c r="B34" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>131523065</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4733,10 +4733,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523060</v>
+        <v>131523068</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448041</v>
+        <v>448070</v>
       </c>
       <c r="R36" t="n">
-        <v>7037312</v>
+        <v>7037546</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4809,11 +4809,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer här på en storvuxen gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4839,14 +4834,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4864,10 +4854,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523068</v>
+        <v>131523060</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4902,10 +4892,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448070</v>
+        <v>448041</v>
       </c>
       <c r="R37" t="n">
-        <v>7037546</v>
+        <v>7037312</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4940,6 +4930,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växer här på en storvuxen gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4965,9 +4960,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4988,7 +4988,7 @@
         <v>131524920</v>
       </c>
       <c r="B38" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>131523036</v>
       </c>
       <c r="B39" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523046</v>
+        <v>131523056</v>
       </c>
       <c r="B40" t="n">
-        <v>57077</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5243,31 +5243,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448205</v>
+        <v>448159</v>
       </c>
       <c r="R40" t="n">
-        <v>7037576</v>
+        <v>7037520</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5313,17 +5308,13 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5332,9 +5323,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5352,55 +5353,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131523048</v>
+        <v>131524933</v>
       </c>
       <c r="B41" t="n">
-        <v>91824</v>
+        <v>80402</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448085</v>
+        <v>448027</v>
       </c>
       <c r="R41" t="n">
-        <v>7037455</v>
+        <v>7037403</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5427,14 +5421,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5443,54 +5442,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131523024</v>
+        <v>131523048</v>
       </c>
       <c r="B42" t="n">
-        <v>91828</v>
+        <v>91825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5498,21 +5471,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5529,10 +5502,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448005</v>
+        <v>448085</v>
       </c>
       <c r="R42" t="n">
-        <v>7037334</v>
+        <v>7037455</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5567,6 +5540,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5594,12 +5572,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5617,10 +5595,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523056</v>
+        <v>131523024</v>
       </c>
       <c r="B43" t="n">
-        <v>79260</v>
+        <v>91829</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5628,26 +5606,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5655,10 +5637,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448159</v>
+        <v>448005</v>
       </c>
       <c r="R43" t="n">
-        <v>7037520</v>
+        <v>7037334</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5718,9 +5700,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5738,48 +5725,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131524933</v>
+        <v>131523046</v>
       </c>
       <c r="B44" t="n">
-        <v>80401</v>
+        <v>57078</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448027</v>
+        <v>448205</v>
       </c>
       <c r="R44" t="n">
-        <v>7037403</v>
+        <v>7037576</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5806,19 +5801,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:55</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5829,16 +5819,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
         <v>131523055</v>
       </c>
       <c r="B45" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131524925</v>
+        <v>131523061</v>
       </c>
       <c r="B46" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5995,19 +5995,22 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448020</v>
+        <v>448093</v>
       </c>
       <c r="R46" t="n">
-        <v>7037318</v>
+        <v>7037386</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6034,54 +6037,65 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131523061</v>
+        <v>131524925</v>
       </c>
       <c r="B47" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6107,22 +6121,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448093</v>
+        <v>448020</v>
       </c>
       <c r="R47" t="n">
-        <v>7037386</v>
+        <v>7037318</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6149,55 +6160,44 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6207,7 +6207,7 @@
         <v>131523047</v>
       </c>
       <c r="B48" t="n">
-        <v>57077</v>
+        <v>57078</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6324,41 +6324,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131523037</v>
+        <v>131523032</v>
       </c>
       <c r="B49" t="n">
-        <v>80401</v>
+        <v>80367</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6366,10 +6362,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448183</v>
+        <v>448050</v>
       </c>
       <c r="R49" t="n">
-        <v>7037535</v>
+        <v>7037306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6406,7 +6402,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en sälg.</t>
+          <t>Enstaka bålar på en rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6426,12 +6422,12 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -6441,7 +6437,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6459,37 +6455,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131523032</v>
+        <v>131523037</v>
       </c>
       <c r="B50" t="n">
-        <v>80366</v>
+        <v>80402</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448050</v>
+        <v>448183</v>
       </c>
       <c r="R50" t="n">
-        <v>7037306</v>
+        <v>7037535</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en rönn.</t>
+          <t>På en sälg.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6590,37 +6590,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131523058</v>
+        <v>131523026</v>
       </c>
       <c r="B51" t="n">
-        <v>79260</v>
+        <v>92552</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6628,10 +6632,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448064</v>
+        <v>448028</v>
       </c>
       <c r="R51" t="n">
-        <v>7037447</v>
+        <v>7037351</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6666,6 +6670,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I stambasen av en levande/döende gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6691,9 +6700,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6711,10 +6725,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131523062</v>
+        <v>131523058</v>
       </c>
       <c r="B52" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6749,10 +6763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448071</v>
+        <v>448064</v>
       </c>
       <c r="R52" t="n">
-        <v>7037345</v>
+        <v>7037447</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6812,14 +6826,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6837,10 +6846,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523054</v>
+        <v>131523062</v>
       </c>
       <c r="B53" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6875,10 +6884,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448187</v>
+        <v>448071</v>
       </c>
       <c r="R53" t="n">
-        <v>7037574</v>
+        <v>7037345</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6938,9 +6947,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6958,41 +6972,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131523026</v>
+        <v>131523054</v>
       </c>
       <c r="B54" t="n">
-        <v>92551</v>
+        <v>79261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7000,10 +7010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448028</v>
+        <v>448187</v>
       </c>
       <c r="R54" t="n">
-        <v>7037351</v>
+        <v>7037574</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7038,11 +7048,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I stambasen av en levande/döende gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7068,14 +7073,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
         <v>131524921</v>
       </c>
       <c r="B55" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>131524934</v>
       </c>
       <c r="B56" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>131523039</v>
       </c>
       <c r="B57" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>131523029</v>
       </c>
       <c r="B12" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>131523040</v>
       </c>
       <c r="B13" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>131524937</v>
       </c>
       <c r="B14" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131523066</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>131524938</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131524923</v>
+        <v>131524936</v>
       </c>
       <c r="B17" t="n">
-        <v>80366</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,21 +2436,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448029</v>
+        <v>448049</v>
       </c>
       <c r="R17" t="n">
-        <v>7037400</v>
+        <v>7037467</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Halvliggande död sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,32 +2537,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131524939</v>
+        <v>131524923</v>
       </c>
       <c r="B18" t="n">
-        <v>80402</v>
+        <v>80369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448190</v>
+        <v>448029</v>
       </c>
       <c r="R18" t="n">
-        <v>7037541</v>
+        <v>7037400</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Halvliggande död sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,32 +2649,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131524936</v>
+        <v>131524939</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>80405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448049</v>
+        <v>448190</v>
       </c>
       <c r="R19" t="n">
-        <v>7037467</v>
+        <v>7037541</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,38 +2761,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523033</v>
+        <v>131523067</v>
       </c>
       <c r="B20" t="n">
-        <v>97900</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2800,10 +2799,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448084</v>
+        <v>448029</v>
       </c>
       <c r="R20" t="n">
-        <v>7037374</v>
+        <v>7037517</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,6 +2850,21 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2868,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523034</v>
+        <v>131523031</v>
       </c>
       <c r="B21" t="n">
-        <v>80366</v>
+        <v>80370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,26 +2893,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2906,7 +2924,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448178</v>
+        <v>448177</v>
       </c>
       <c r="R21" t="n">
         <v>7037486</v>
@@ -2946,7 +2964,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växer här på en grovbarkad gammal sälg.</t>
+          <t>På en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,10 +3017,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131523067</v>
+        <v>131523034</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3010,21 +3028,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3037,10 +3055,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448029</v>
+        <v>448178</v>
       </c>
       <c r="R22" t="n">
-        <v>7037517</v>
+        <v>7037486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3075,6 +3093,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3092,17 +3115,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3120,41 +3148,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523031</v>
+        <v>131523033</v>
       </c>
       <c r="B23" t="n">
-        <v>80367</v>
+        <v>97903</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3162,10 +3187,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448177</v>
+        <v>448084</v>
       </c>
       <c r="R23" t="n">
-        <v>7037486</v>
+        <v>7037374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3200,11 +3225,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3218,26 +3238,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
         <v>131523069</v>
       </c>
       <c r="B24" t="n">
-        <v>80401</v>
+        <v>80404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131524924</v>
+        <v>131523059</v>
       </c>
       <c r="B25" t="n">
-        <v>80367</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,37 +3401,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448025</v>
+        <v>448126</v>
       </c>
       <c r="R25" t="n">
-        <v>7037401</v>
+        <v>7037416</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3458,54 +3461,60 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gammal låga, under död sälg med lunglav</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131523059</v>
+        <v>131524927</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3531,22 +3540,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448126</v>
+        <v>448032</v>
       </c>
       <c r="R26" t="n">
-        <v>7037416</v>
+        <v>7037303</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3573,60 +3579,54 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131524927</v>
+        <v>131524932</v>
       </c>
       <c r="B27" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448032</v>
+        <v>448026</v>
       </c>
       <c r="R27" t="n">
-        <v>7037303</v>
+        <v>7037380</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3703,12 +3703,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3735,55 +3730,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131523041</v>
+        <v>131524924</v>
       </c>
       <c r="B28" t="n">
-        <v>80402</v>
+        <v>80370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448051</v>
+        <v>448025</v>
       </c>
       <c r="R28" t="n">
-        <v>7037306</v>
+        <v>7037401</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3810,14 +3798,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en rönn.</t>
+          <t>Gammal låga, under död sälg med lunglav</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,92 +3824,73 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131524932</v>
+        <v>131523041</v>
       </c>
       <c r="B29" t="n">
-        <v>79261</v>
+        <v>80405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448026</v>
+        <v>448051</v>
       </c>
       <c r="R29" t="n">
-        <v>7037380</v>
+        <v>7037306</v>
       </c>
       <c r="S29" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3938,19 +3917,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3959,18 +3933,44 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
         <v>131523035</v>
       </c>
       <c r="B30" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>131524919</v>
       </c>
       <c r="B31" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>131523030</v>
       </c>
       <c r="B32" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>131524935</v>
       </c>
       <c r="B33" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>131523049</v>
       </c>
       <c r="B34" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>131523065</v>
       </c>
       <c r="B35" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>131523068</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>131523060</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>131524920</v>
       </c>
       <c r="B38" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>131523036</v>
       </c>
       <c r="B39" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523056</v>
+        <v>131523046</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>57081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5243,26 +5243,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448159</v>
+        <v>448205</v>
       </c>
       <c r="R40" t="n">
-        <v>7037520</v>
+        <v>7037576</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5308,13 +5313,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5323,19 +5332,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5353,48 +5352,51 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131524933</v>
+        <v>131523056</v>
       </c>
       <c r="B41" t="n">
-        <v>80402</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448027</v>
+        <v>448159</v>
       </c>
       <c r="R41" t="n">
-        <v>7037403</v>
+        <v>7037520</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5421,39 +5423,50 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5463,7 +5476,7 @@
         <v>131523048</v>
       </c>
       <c r="B42" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5598,7 +5611,7 @@
         <v>131523024</v>
       </c>
       <c r="B43" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5725,56 +5738,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131523046</v>
+        <v>131524933</v>
       </c>
       <c r="B44" t="n">
-        <v>57078</v>
+        <v>80405</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448205</v>
+        <v>448027</v>
       </c>
       <c r="R44" t="n">
-        <v>7037576</v>
+        <v>7037403</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5801,14 +5806,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5819,26 +5829,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
         <v>131523055</v>
       </c>
       <c r="B45" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131523061</v>
+        <v>131523047</v>
       </c>
       <c r="B46" t="n">
-        <v>79261</v>
+        <v>57081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5977,26 +5977,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6004,10 +6009,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448093</v>
+        <v>448216</v>
       </c>
       <c r="R46" t="n">
-        <v>7037386</v>
+        <v>7037540</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6042,13 +6047,17 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6057,24 +6066,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6092,10 +6086,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131524925</v>
+        <v>131523061</v>
       </c>
       <c r="B47" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,19 +6115,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448020</v>
+        <v>448093</v>
       </c>
       <c r="R47" t="n">
-        <v>7037318</v>
+        <v>7037386</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6160,54 +6157,65 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131523047</v>
+        <v>131524925</v>
       </c>
       <c r="B48" t="n">
-        <v>57078</v>
+        <v>79264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6215,45 +6223,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448216</v>
+        <v>448020</v>
       </c>
       <c r="R48" t="n">
-        <v>7037540</v>
+        <v>7037318</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6280,14 +6280,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6298,26 +6308,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
         <v>131523032</v>
       </c>
       <c r="B49" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>131523037</v>
       </c>
       <c r="B50" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>131523026</v>
       </c>
       <c r="B51" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>131523058</v>
       </c>
       <c r="B52" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>131523062</v>
       </c>
       <c r="B53" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>131523054</v>
       </c>
       <c r="B54" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131524921</v>
+        <v>131524934</v>
       </c>
       <c r="B55" t="n">
-        <v>91849</v>
+        <v>91832</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7104,19 +7104,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7124,13 +7128,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>448016</v>
+        <v>448037</v>
       </c>
       <c r="R55" t="n">
-        <v>7037409</v>
+        <v>7037451</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7159,7 +7163,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7169,7 +7173,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7196,10 +7200,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131524934</v>
+        <v>131524921</v>
       </c>
       <c r="B56" t="n">
-        <v>91829</v>
+        <v>91852</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,23 +7211,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>448037</v>
+        <v>448016</v>
       </c>
       <c r="R56" t="n">
-        <v>7037451</v>
+        <v>7037409</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7306,7 +7306,7 @@
         <v>131523039</v>
       </c>
       <c r="B57" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103454395</v>
+        <v>131523048</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448097.3564878901</v>
+        <v>448085</v>
       </c>
       <c r="R2" t="n">
-        <v>7037522.164752672</v>
+        <v>7037455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,30 +770,50 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103454382</v>
+        <v>131523049</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,34 +821,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448221.9675758682</v>
+        <v>447992</v>
       </c>
       <c r="R3" t="n">
-        <v>7037555.92331142</v>
+        <v>7037352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,22 +882,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,30 +905,50 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103454385</v>
+        <v>103454384</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +956,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448126.4466543338</v>
+        <v>448188</v>
       </c>
       <c r="R4" t="n">
-        <v>7037520.797324237</v>
+        <v>7037580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,19 +1013,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103454397</v>
+        <v>103454391</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448163.4949486132</v>
+        <v>448134</v>
       </c>
       <c r="R5" t="n">
-        <v>7037513.038974883</v>
+        <v>7037482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,19 +1111,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103454377</v>
+        <v>103454396</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448042.867797371</v>
+        <v>448074</v>
       </c>
       <c r="R6" t="n">
-        <v>7037476.533588285</v>
+        <v>7037413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,19 +1209,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1239,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103454370</v>
+        <v>103454397</v>
       </c>
       <c r="B7" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448175.0230499597</v>
+        <v>448164</v>
       </c>
       <c r="R7" t="n">
-        <v>7037533.426703211</v>
+        <v>7037513</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,19 +1307,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103454386</v>
+        <v>131523024</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,34 +1348,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448054.2435067447</v>
+        <v>448005</v>
       </c>
       <c r="R8" t="n">
-        <v>7037542.546368834</v>
+        <v>7037334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,22 +1409,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,30 +1427,50 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103454384</v>
+        <v>131524934</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448187.4269993959</v>
+        <v>448037</v>
       </c>
       <c r="R9" t="n">
-        <v>7037580.189317226</v>
+        <v>7037451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,22 +1532,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,34 +1556,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103454396</v>
+        <v>131523031</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,34 +1585,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448073.6339130378</v>
+        <v>448177</v>
       </c>
       <c r="R10" t="n">
-        <v>7037412.964771684</v>
+        <v>7037486</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,22 +1646,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,30 +1669,50 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103454391</v>
+        <v>131523032</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,34 +1720,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448133.8888456714</v>
+        <v>448050</v>
       </c>
       <c r="R11" t="n">
-        <v>7037482.657260883</v>
+        <v>7037306</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,22 +1777,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,70 +1800,88 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131523029</v>
+        <v>131524924</v>
       </c>
       <c r="B12" t="n">
-        <v>80410</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448180</v>
+        <v>448025</v>
       </c>
       <c r="R12" t="n">
-        <v>7037489</v>
+        <v>7037401</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,14 +1908,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en grovbarkad gammal sälg.</t>
+          <t>Gammal låga, under död sälg med lunglav</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,54 +1934,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131523040</v>
+        <v>131523026</v>
       </c>
       <c r="B13" t="n">
-        <v>80417</v>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,28 +1963,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1982,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448178</v>
+        <v>448028</v>
       </c>
       <c r="R13" t="n">
-        <v>7037487</v>
+        <v>7037351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2034,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en grovbarkad gammal sälg.</t>
+          <t>I stambasen av en levande/döende gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,22 +2054,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2075,14 +2087,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131524937</v>
+        <v>103454382</v>
       </c>
       <c r="B14" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2106,17 +2118,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448113</v>
+        <v>448222</v>
       </c>
       <c r="R14" t="n">
-        <v>7037466</v>
+        <v>7037556</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2140,22 +2152,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,32 +2166,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131523066</v>
+        <v>103454386</v>
       </c>
       <c r="B15" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2211,19 +2214,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448004</v>
+        <v>448054</v>
       </c>
       <c r="R15" t="n">
-        <v>7037485</v>
+        <v>7037543</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,17 +2250,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer här på flera granar.</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,54 +2268,29 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131524938</v>
+        <v>131523052</v>
       </c>
       <c r="B16" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2342,19 +2312,22 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448127</v>
+        <v>448259</v>
       </c>
       <c r="R16" t="n">
-        <v>7037481</v>
+        <v>7037550</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,92 +2354,101 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131524923</v>
+        <v>131523053</v>
       </c>
       <c r="B17" t="n">
-        <v>80381</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448029</v>
+        <v>448247</v>
       </c>
       <c r="R17" t="n">
-        <v>7037400</v>
+        <v>7037562</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,92 +2475,101 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Halvliggande död sälg</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131524939</v>
+        <v>131523054</v>
       </c>
       <c r="B18" t="n">
-        <v>80417</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448190</v>
+        <v>448187</v>
       </c>
       <c r="R18" t="n">
-        <v>7037541</v>
+        <v>7037574</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2605,58 +2596,64 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131524936</v>
+        <v>131523055</v>
       </c>
       <c r="B19" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2678,19 +2675,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448049</v>
+        <v>448153</v>
       </c>
       <c r="R19" t="n">
-        <v>7037467</v>
+        <v>7037556</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,82 +2717,87 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131523033</v>
+        <v>131523056</v>
       </c>
       <c r="B20" t="n">
-        <v>97919</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2800,10 +2805,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448084</v>
+        <v>448159</v>
       </c>
       <c r="R20" t="n">
-        <v>7037374</v>
+        <v>7037520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,6 +2856,21 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2868,32 +2888,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131523034</v>
+        <v>131523057</v>
       </c>
       <c r="B21" t="n">
-        <v>80381</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,10 +2926,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448178</v>
+        <v>448179</v>
       </c>
       <c r="R21" t="n">
-        <v>7037486</v>
+        <v>7037454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2946,7 +2966,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växer här på en grovbarkad gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,22 +2986,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2999,14 +3014,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131523067</v>
+        <v>131523058</v>
       </c>
       <c r="B22" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3037,10 +3052,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448029</v>
+        <v>448064</v>
       </c>
       <c r="R22" t="n">
-        <v>7037517</v>
+        <v>7037447</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3120,41 +3135,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523031</v>
+        <v>131523059</v>
       </c>
       <c r="B23" t="n">
-        <v>80382</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3162,10 +3173,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448177</v>
+        <v>448126</v>
       </c>
       <c r="R23" t="n">
-        <v>7037486</v>
+        <v>7037416</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3200,11 +3211,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3222,22 +3228,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3255,27 +3256,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131523069</v>
+        <v>131523060</v>
       </c>
       <c r="B24" t="n">
-        <v>80416</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3285,11 +3286,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3297,10 +3294,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448178</v>
+        <v>448041</v>
       </c>
       <c r="R24" t="n">
-        <v>7037491</v>
+        <v>7037312</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3337,7 +3334,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer här på en grovbarkad gammal sälg.</t>
+          <t>Växer här på en storvuxen gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3357,22 +3354,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3390,14 +3387,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131523059</v>
+        <v>131523061</v>
       </c>
       <c r="B25" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3428,10 +3425,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448126</v>
+        <v>448093</v>
       </c>
       <c r="R25" t="n">
-        <v>7037416</v>
+        <v>7037386</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,9 +3488,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3511,14 +3513,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131524927</v>
+        <v>131523062</v>
       </c>
       <c r="B26" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3540,19 +3542,22 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448032</v>
+        <v>448071</v>
       </c>
       <c r="R26" t="n">
-        <v>7037303</v>
+        <v>7037345</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3579,85 +3584,92 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131523041</v>
+        <v>131523064</v>
       </c>
       <c r="B27" t="n">
-        <v>80417</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3665,10 +3677,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448051</v>
+        <v>447974</v>
       </c>
       <c r="R27" t="n">
-        <v>7037306</v>
+        <v>7037406</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,11 +3715,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På en rönn.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3725,22 +3732,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3758,14 +3765,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131524932</v>
+        <v>131523065</v>
       </c>
       <c r="B28" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3787,19 +3794,22 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448026</v>
+        <v>447990</v>
       </c>
       <c r="R28" t="n">
-        <v>7037380</v>
+        <v>7037451</v>
       </c>
       <c r="S28" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3826,19 +3836,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3847,66 +3852,95 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131524924</v>
+        <v>131523066</v>
       </c>
       <c r="B29" t="n">
-        <v>80382</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448025</v>
+        <v>448004</v>
       </c>
       <c r="R29" t="n">
-        <v>7037401</v>
+        <v>7037485</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3933,24 +3967,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gammal låga, under död sälg med lunglav</t>
+          <t>Växer här på flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3959,50 +3983,76 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131523035</v>
+        <v>131523067</v>
       </c>
       <c r="B30" t="n">
-        <v>80381</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4015,10 +4065,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448050</v>
+        <v>448029</v>
       </c>
       <c r="R30" t="n">
-        <v>7037306</v>
+        <v>7037517</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4053,11 +4103,6 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en rönn.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4075,22 +4120,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4108,14 +4148,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131524919</v>
+        <v>131523068</v>
       </c>
       <c r="B31" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4137,19 +4177,22 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448031</v>
+        <v>448070</v>
       </c>
       <c r="R31" t="n">
-        <v>7037527</v>
+        <v>7037546</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4176,99 +4219,98 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131523030</v>
+        <v>131524919</v>
       </c>
       <c r="B32" t="n">
-        <v>80410</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447993</v>
+        <v>448031</v>
       </c>
       <c r="R32" t="n">
-        <v>7037446</v>
+        <v>7037527</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4295,14 +4337,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4311,76 +4363,50 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131524935</v>
+        <v>131524925</v>
       </c>
       <c r="B33" t="n">
-        <v>80381</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4390,10 +4416,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>448054</v>
+        <v>448020</v>
       </c>
       <c r="R33" t="n">
-        <v>7037460</v>
+        <v>7037318</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4425,7 +4451,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4435,12 +4461,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På liten torraka av rönn.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4467,55 +4493,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131523049</v>
+        <v>131524926</v>
       </c>
       <c r="B34" t="n">
-        <v>91844</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447992</v>
+        <v>448025</v>
       </c>
       <c r="R34" t="n">
-        <v>7037352</v>
+        <v>7037289</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4542,14 +4561,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4558,58 +4587,32 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131523065</v>
+        <v>131524927</v>
       </c>
       <c r="B35" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4631,22 +4634,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447990</v>
+        <v>448032</v>
       </c>
       <c r="R35" t="n">
-        <v>7037451</v>
+        <v>7037303</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4673,14 +4673,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hyfsar gott om bålar på en stående död gran med full längd.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4689,58 +4699,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131523068</v>
+        <v>131524931</v>
       </c>
       <c r="B36" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4762,22 +4746,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448070</v>
+        <v>447982</v>
       </c>
       <c r="R36" t="n">
-        <v>7037546</v>
+        <v>7037373</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4804,64 +4785,58 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran-torraka</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131523060</v>
+        <v>131524932</v>
       </c>
       <c r="B37" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4883,22 +4858,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448041</v>
+        <v>448026</v>
       </c>
       <c r="R37" t="n">
-        <v>7037312</v>
+        <v>7037380</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4925,14 +4897,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växer här på en storvuxen gran.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4941,97 +4918,66 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131524920</v>
+        <v>131524936</v>
       </c>
       <c r="B38" t="n">
-        <v>58073</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448020</v>
+        <v>448049</v>
       </c>
       <c r="R38" t="n">
-        <v>7037494</v>
+        <v>7037467</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5060,7 +5006,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5070,7 +5016,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5097,55 +5048,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131523036</v>
+        <v>131524937</v>
       </c>
       <c r="B39" t="n">
-        <v>80381</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447991</v>
+        <v>448113</v>
       </c>
       <c r="R39" t="n">
-        <v>7037445</v>
+        <v>7037466</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5172,14 +5116,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På en klen rönn.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5188,58 +5137,32 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131523056</v>
+        <v>131524938</v>
       </c>
       <c r="B40" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5261,22 +5184,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448159</v>
+        <v>448127</v>
       </c>
       <c r="R40" t="n">
-        <v>7037520</v>
+        <v>7037481</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5303,82 +5223,76 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131524933</v>
+        <v>131524941</v>
       </c>
       <c r="B41" t="n">
-        <v>80417</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5388,10 +5302,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448027</v>
+        <v>448235</v>
       </c>
       <c r="R41" t="n">
-        <v>7037403</v>
+        <v>7037540</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5423,7 +5337,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5433,7 +5347,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5460,10 +5374,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131523048</v>
+        <v>131523034</v>
       </c>
       <c r="B42" t="n">
-        <v>91844</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5471,30 +5385,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5502,10 +5412,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448085</v>
+        <v>448178</v>
       </c>
       <c r="R42" t="n">
-        <v>7037455</v>
+        <v>7037486</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5542,7 +5452,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i stambasen av en stående döende gran.</t>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5562,22 +5472,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5595,10 +5505,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131523024</v>
+        <v>131523035</v>
       </c>
       <c r="B43" t="n">
-        <v>91848</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,30 +5516,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5637,10 +5543,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448005</v>
+        <v>448050</v>
       </c>
       <c r="R43" t="n">
-        <v>7037334</v>
+        <v>7037306</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5675,6 +5581,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5692,22 +5603,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5725,10 +5636,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131523046</v>
+        <v>131523036</v>
       </c>
       <c r="B44" t="n">
-        <v>57093</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5736,29 +5647,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5768,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448205</v>
+        <v>447991</v>
       </c>
       <c r="R44" t="n">
-        <v>7037576</v>
+        <v>7037445</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5808,7 +5718,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5817,6 +5727,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5825,9 +5736,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5845,10 +5771,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131523055</v>
+        <v>131524923</v>
       </c>
       <c r="B45" t="n">
-        <v>79276</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5856,40 +5782,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448153</v>
+        <v>448029</v>
       </c>
       <c r="R45" t="n">
-        <v>7037556</v>
+        <v>7037400</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5916,60 +5839,54 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Halvliggande död sälg</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131523047</v>
+        <v>131524928</v>
       </c>
       <c r="B46" t="n">
-        <v>57093</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5977,45 +5894,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448216</v>
+        <v>447976</v>
       </c>
       <c r="R46" t="n">
-        <v>7037540</v>
+        <v>7037362</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6042,14 +5951,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6060,36 +5979,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131523061</v>
+        <v>131524935</v>
       </c>
       <c r="B47" t="n">
-        <v>79276</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6097,40 +6006,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448093</v>
+        <v>448054</v>
       </c>
       <c r="R47" t="n">
-        <v>7037386</v>
+        <v>7037460</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6157,103 +6063,99 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På liten torraka av rönn.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131524925</v>
+        <v>131523029</v>
       </c>
       <c r="B48" t="n">
-        <v>79276</v>
+        <v>80461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448020</v>
+        <v>448180</v>
       </c>
       <c r="R48" t="n">
-        <v>7037318</v>
+        <v>7037489</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6280,24 +6182,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6306,28 +6198,54 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131523037</v>
+        <v>131523030</v>
       </c>
       <c r="B49" t="n">
-        <v>80417</v>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6335,21 +6253,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6366,10 +6284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448183</v>
+        <v>447993</v>
       </c>
       <c r="R49" t="n">
-        <v>7037535</v>
+        <v>7037446</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6406,7 +6324,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en sälg.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6426,12 +6344,12 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -6441,7 +6359,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6459,51 +6377,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131523032</v>
+        <v>131524930</v>
       </c>
       <c r="B50" t="n">
-        <v>80382</v>
+        <v>80461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448050</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>7037306</v>
+        <v>7037362</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6530,14 +6445,24 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en rönn.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6546,71 +6471,45 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131523062</v>
+        <v>131523069</v>
       </c>
       <c r="B51" t="n">
-        <v>79276</v>
+        <v>80467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6620,7 +6519,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6628,10 +6531,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448071</v>
+        <v>448178</v>
       </c>
       <c r="R51" t="n">
-        <v>7037345</v>
+        <v>7037491</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6666,6 +6569,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Växer här på en grovbarkad gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6683,22 +6591,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6716,10 +6624,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131523026</v>
+        <v>103454370</v>
       </c>
       <c r="B52" t="n">
-        <v>92571</v>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6727,41 +6635,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448028</v>
+        <v>448175</v>
       </c>
       <c r="R52" t="n">
-        <v>7037351</v>
+        <v>7037533</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6788,17 +6689,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I stambasen av en levande/döende gran.</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6811,77 +6707,56 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131523054</v>
+        <v>131523037</v>
       </c>
       <c r="B53" t="n">
-        <v>79276</v>
+        <v>80468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6889,10 +6764,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448187</v>
+        <v>448183</v>
       </c>
       <c r="R53" t="n">
-        <v>7037574</v>
+        <v>7037535</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6927,6 +6802,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en sälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6944,17 +6824,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6972,37 +6857,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131523058</v>
+        <v>131523039</v>
       </c>
       <c r="B54" t="n">
-        <v>79276</v>
+        <v>80468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7010,10 +6899,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448064</v>
+        <v>448193</v>
       </c>
       <c r="R54" t="n">
-        <v>7037447</v>
+        <v>7037544</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7048,6 +6937,11 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På en rönnlåga.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7065,17 +6959,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7093,45 +6992,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131524934</v>
+        <v>131523040</v>
       </c>
       <c r="B55" t="n">
-        <v>91848</v>
+        <v>80468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>448037</v>
+        <v>448178</v>
       </c>
       <c r="R55" t="n">
-        <v>7037451</v>
+        <v>7037487</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7161,19 +7067,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:10</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7182,62 +7083,99 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131524921</v>
+        <v>131523041</v>
       </c>
       <c r="B56" t="n">
-        <v>91868</v>
+        <v>80468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>448016</v>
+        <v>448051</v>
       </c>
       <c r="R56" t="n">
-        <v>7037409</v>
+        <v>7037306</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7264,19 +7202,14 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:42</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7285,28 +7218,54 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131523039</v>
+        <v>131524933</v>
       </c>
       <c r="B57" t="n">
-        <v>80417</v>
+        <v>80468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7332,26 +7291,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hällberget Nordöst, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>448193</v>
+        <v>448027</v>
       </c>
       <c r="R57" t="n">
-        <v>7037544</v>
+        <v>7037403</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7378,14 +7330,19 @@
           <t>2026-03-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På en rönnlåga.</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7394,47 +7351,788 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131524939</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>448190</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7037541</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131523046</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>448205</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7037576</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131523047</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>448216</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7037540</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med inslag av björk, sälg och rönn.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131524920</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>448020</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7037494</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131523033</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hällberget Nordöst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>448084</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7037374</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>103454395</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>448098</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7037522</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>103454379</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>447990</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7037407</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4696-2026 artfynd.xlsx
+++ b/artfynd/A 4696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -933,6 +943,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523032</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1064,6 +1079,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523060</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524925</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1288,6 +1313,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524926</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1531,6 +1566,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523035</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1666,6 +1706,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523041</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1801,6 +1846,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1936,6 +1986,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523049</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2034,6 +2089,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454384</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2132,6 +2192,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454391</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2230,6 +2295,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454396</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2328,6 +2398,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454397</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2435,6 +2510,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524934</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2570,6 +2650,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523031</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2682,6 +2767,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524924</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2817,6 +2907,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2915,6 +3010,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454382</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3013,6 +3113,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454386</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3134,6 +3239,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523052</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3255,6 +3365,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523053</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3376,6 +3491,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523054</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3497,6 +3617,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523055</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3618,6 +3743,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523056</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3744,6 +3874,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523057</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3865,6 +4000,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523058</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3986,6 +4126,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523059</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4112,6 +4257,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523061</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4238,6 +4388,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523062</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4364,6 +4519,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523064</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4495,6 +4655,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523065</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4626,6 +4791,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523066</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4747,6 +4917,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523067</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4868,6 +5043,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523068</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4980,6 +5160,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524919</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5092,6 +5277,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524931</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5199,6 +5389,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524932</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5311,6 +5506,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524936</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5418,6 +5618,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524937</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5530,6 +5735,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524938</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5637,6 +5847,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524941</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5768,6 +5983,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523034</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5903,6 +6123,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523036</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6015,6 +6240,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524923</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6127,6 +6357,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524928</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6239,6 +6474,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524935</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6374,6 +6614,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523029</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6509,6 +6754,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523030</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6621,6 +6871,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524930</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6756,6 +7011,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523069</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6854,6 +7114,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454370</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6989,6 +7254,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523037</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7124,6 +7394,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523039</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7259,6 +7534,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523040</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7366,6 +7646,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524933</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7478,6 +7763,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524939</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7598,6 +7888,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523046</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7718,6 +8013,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523047</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7830,6 +8130,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131524920</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7937,6 +8242,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523033</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8035,6 +8345,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454395</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8133,8 +8448,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103454379</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>